--- a/docs/ValueSet-ahip-outreach-mode.xlsx
+++ b/docs/ValueSet-ahip-outreach-mode.xlsx
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Outreach Modes</t>
+    <t>Used as the answer options for the outreach preferences question in the Language Section, capturing a patient's preferred channels for health care outreach.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -106,25 +106,25 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>E</t>
+    <t>EMAILWRIT</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>P</t>
+    <t>PHONE</t>
   </si>
   <si>
     <t>Phone Call</t>
   </si>
   <si>
-    <t>M</t>
+    <t>MAILWRIT</t>
   </si>
   <si>
     <t>Mailed Letter</t>
   </si>
   <si>
-    <t>T</t>
+    <t>MSGWRIT</t>
   </si>
   <si>
     <t>Text Message</t>
@@ -133,7 +133,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-outreach-modes</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ParticipationMode</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -142,7 +142,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-ahip-outreach-mode.xlsx
+++ b/docs/ValueSet-ahip-outreach-mode.xlsx
@@ -94,7 +94,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -142,7 +143,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
